--- a/artfynd/A 42509-2021 artfynd.xlsx
+++ b/artfynd/A 42509-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42509-2021 artfynd.xlsx
+++ b/artfynd/A 42509-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83572008</v>
+        <v>54570235</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107719</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>220015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Hässleklocka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Campanula latifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,24 +703,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ask (Skyddsvärt träd), Vg</t>
+          <t>lund vid vägen, Jonstorp, Vilske-Kleva, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409963.5965674369</v>
+        <v>409791</v>
       </c>
       <c r="R2" t="n">
-        <v>6453819.640027658</v>
+        <v>6453746</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,34 +738,19 @@
           <t>Vilske-Kleva</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>5EF3FFDC-62F7-42F8-A3FF-25E39AE8195C</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-08-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-08-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>{10DAE06B-126C-4C6C-BF4B-F9691F946F34}</t>
+          <t>lite</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,19 +765,630 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>54570233</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>lund vid vägen, Jonstorp, Vilske-Kleva, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>409791</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6453746</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vilske-Kleva</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2014-09-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2014-09-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>83572008</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>409964</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6453820</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vilske-Kleva</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5EF3FFDC-62F7-42F8-A3FF-25E39AE8195C</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2011-08-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2011-08-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>{10DAE06B-126C-4C6C-BF4B-F9691F946F34}</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Anna Stenström</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Anna Stenström, Vikki Bengtsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>54570236</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106061</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221101</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Springkorn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Impatiens noli-tangere</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>lund vid vägen, Jonstorp, Vilske-Kleva, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>409791</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6453746</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vilske-Kleva</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2014-09-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2014-09-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ett bestånd</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>54570579</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106329</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>lund vid vägen, Jonstorp, Vilske-Kleva, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>409791</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6453746</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vilske-Kleva</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2015-06-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2015-06-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>i vägkanten, talrik. Även i trädgården mittemot.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>54570595</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>lund vid vägen, Jonstorp, Vilske-Kleva, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>409791</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6453746</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vilske-Kleva</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2015-06-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2015-06-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>fåtalig</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>54570234</v>
+      </c>
+      <c r="B8" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>lund vid vägen, Jonstorp, Vilske-Kleva, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>409791</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6453746</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vilske-Kleva</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2014-09-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2014-09-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
